--- a/exports-revit/EHPAD_Bouches_Ventilation.xlsx
+++ b/exports-revit/EHPAD_Bouches_Ventilation.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5200" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5200" uniqueCount="862">
   <si>
     <t xml:space="preserve">Bouches de ventilation – contrôle par rapport au dossier DCE</t>
   </si>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">• Les modèles suivent le CCTP : GADD F (chambres), ALYZE S (salles de bains et VMC), DCFD-F et DATP (locaux communs).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Écarts assumés et suite à donner : onglet « Écarts au CCTP » (flexibles, régulateurs, débit CTA 5, réseau VMC à dessiner).</t>
+    <t xml:space="preserve">• Écarts assumés et suite à donner : onglet « Écarts au CCTP » (flexibles, régulateurs, débit CTA 5, grilles de transfert des offices).</t>
   </si>
   <si>
     <t xml:space="preserve">Repère</t>
@@ -1824,7 +1824,7 @@
     <t xml:space="preserve">CCTP 4.12.5</t>
   </si>
   <si>
-    <t xml:space="preserve">Réseau VMC sanitaires (caisson + gaines) à créer</t>
+    <t xml:space="preserve">Raccordée au caisson VMC 2</t>
   </si>
   <si>
     <t xml:space="preserve">L001</t>
@@ -1836,6 +1836,9 @@
     <t xml:space="preserve">Wc</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 2 ; bouche décalée dans le local (gaine CTA ou poutre au-dessus)</t>
+  </si>
+  <si>
     <t xml:space="preserve">L002</t>
   </si>
   <si>
@@ -1866,6 +1869,9 @@
     <t xml:space="preserve">déc.</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">L093</t>
   </si>
   <si>
@@ -1887,6 +1893,9 @@
     <t xml:space="preserve">EXT01</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">L007</t>
   </si>
   <si>
@@ -1896,6 +1905,9 @@
     <t xml:space="preserve">linge S</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">L049</t>
   </si>
   <si>
@@ -1923,6 +1935,9 @@
     <t xml:space="preserve">mén.</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 4 ; bouche décalée dans le local (gaine CTA ou poutre au-dessus)</t>
+  </si>
+  <si>
     <t xml:space="preserve">L011</t>
   </si>
   <si>
@@ -1947,6 +1962,9 @@
     <t xml:space="preserve">office</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 1 ; bouche décalée dans le local (gaine CTA ou poutre au-dessus)</t>
+  </si>
+  <si>
     <t xml:space="preserve">L051</t>
   </si>
   <si>
@@ -2067,6 +2085,9 @@
     <t xml:space="preserve">LOG06</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 3 ; bouche décalée dans le local (gaine CTA ou poutre au-dessus)</t>
+  </si>
+  <si>
     <t xml:space="preserve">L141</t>
   </si>
   <si>
@@ -2160,6 +2181,9 @@
     <t xml:space="preserve">PAS329</t>
   </si>
   <si>
+    <t xml:space="preserve">Raccordée au caisson VMC 6</t>
+  </si>
+  <si>
     <t xml:space="preserve">L215</t>
   </si>
   <si>
@@ -2541,10 +2565,10 @@
     <t xml:space="preserve">CCTP 4.12 : caisson d'extraction C4 en toiture, gaines, bouches autoréglables</t>
   </si>
   <si>
-    <t xml:space="preserve">46 bouches posées avec leur débit (3 090 m³/h) ; caissons et gaines pas encore dessinés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prochaine étape : réseau VMC (caissons, gaines, antennes).</t>
+    <t xml:space="preserve">6 caissons C4 en toiture (VMC 1 à 6), montées, collecteurs et antennes rigides : les 46 bouches (3 090 m³/h) sont raccordées</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejets à plus de 8 m des prises d'air neuf des CTA (vérifié). Caissons VMC 2 et VMC 4 : posés en rive, à caler avec l'acrotère.</t>
   </si>
   <si>
     <t xml:space="preserve">Compensation des sanitaires</t>
@@ -2553,10 +2577,10 @@
     <t xml:space="preserve">CCTP 4.12.6 : détalonnage &lt; 120 m³/h, bouches de transfert au-delà</t>
   </si>
   <si>
-    <t xml:space="preserve">Offices et tisanerie (450 m³/h) : compensation par bouches de transfert à prévoir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À ajouter avec le réseau VMC.</t>
+    <t xml:space="preserve">Offices et tisanerie (450 m³/h chacun) : bouches de transfert (grilles en porte ou en cloison) ; locaux &lt; 120 m³/h : détalonnage des portes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grilles de transfert à commander avec les menuiseries ; pas dessinées dans la maquette CVC.</t>
   </si>
   <si>
     <t xml:space="preserve">Hypothèses</t>
@@ -3423,11 +3447,11 @@
       </c>
       <c r="E15" s="4" t="n">
         <f aca="false">COUNTIFS(Bouches!$B$2:$B$271,A15,Bouches!$C$2:$C$271,B15,Bouches!$Q$2:$Q$271,"oui")</f>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4" t="n">
         <f aca="false">C15-E15</f>
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,11 +3468,11 @@
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">SUM(E5:E15)</f>
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="F16" s="7" t="n">
         <f aca="false">SUM(F5:F15)</f>
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17138,10 +17162,10 @@
         <f aca="false">IF(O226&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q226" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R226" s="13" t="s">
+      <c r="Q226" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R226" s="4" t="s">
         <v>598</v>
       </c>
       <c r="S226" s="12" t="s">
@@ -17200,19 +17224,19 @@
         <f aca="false">IF(O227&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q227" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R227" s="13" t="s">
-        <v>598</v>
+      <c r="Q227" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R227" s="4" t="s">
+        <v>602</v>
       </c>
       <c r="S227" s="12" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>16</v>
@@ -17224,10 +17248,10 @@
         <v>42</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>45</v>
@@ -17262,19 +17286,19 @@
         <f aca="false">IF(O228&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q228" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R228" s="13" t="s">
-        <v>598</v>
+      <c r="Q228" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R228" s="4" t="s">
+        <v>602</v>
       </c>
       <c r="S228" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>16</v>
@@ -17286,10 +17310,10 @@
         <v>42</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>45</v>
@@ -17324,19 +17348,19 @@
         <f aca="false">IF(O229&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q229" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R229" s="13" t="s">
-        <v>598</v>
+      <c r="Q229" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R229" s="4" t="s">
+        <v>602</v>
       </c>
       <c r="S229" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>16</v>
@@ -17348,10 +17372,10 @@
         <v>42</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>45</v>
@@ -17386,19 +17410,19 @@
         <f aca="false">IF(O230&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q230" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R230" s="13" t="s">
-        <v>598</v>
+      <c r="Q230" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R230" s="4" t="s">
+        <v>613</v>
       </c>
       <c r="S230" s="12" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>16</v>
@@ -17410,10 +17434,10 @@
         <v>42</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>45</v>
@@ -17448,19 +17472,19 @@
         <f aca="false">IF(O231&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q231" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R231" s="13" t="s">
-        <v>598</v>
+      <c r="Q231" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R231" s="4" t="s">
+        <v>613</v>
       </c>
       <c r="S231" s="12" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>16</v>
@@ -17472,10 +17496,10 @@
         <v>42</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>45</v>
@@ -17510,19 +17534,19 @@
         <f aca="false">IF(O232&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q232" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R232" s="13" t="s">
-        <v>598</v>
+      <c r="Q232" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R232" s="4" t="s">
+        <v>621</v>
       </c>
       <c r="S232" s="12" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>16</v>
@@ -17534,10 +17558,10 @@
         <v>42</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>45</v>
@@ -17572,19 +17596,19 @@
         <f aca="false">IF(O233&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q233" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R233" s="13" t="s">
-        <v>598</v>
+      <c r="Q233" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R233" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S233" s="12" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>16</v>
@@ -17596,10 +17620,10 @@
         <v>42</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>45</v>
@@ -17634,19 +17658,19 @@
         <f aca="false">IF(O234&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q234" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R234" s="13" t="s">
-        <v>598</v>
+      <c r="Q234" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R234" s="4" t="s">
+        <v>602</v>
       </c>
       <c r="S234" s="12" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>16</v>
@@ -17658,10 +17682,10 @@
         <v>42</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>45</v>
@@ -17696,19 +17720,19 @@
         <f aca="false">IF(O235&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q235" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R235" s="13" t="s">
-        <v>598</v>
+      <c r="Q235" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R235" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S235" s="12" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>16</v>
@@ -17720,10 +17744,10 @@
         <v>42</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>45</v>
@@ -17758,19 +17782,19 @@
         <f aca="false">IF(O236&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q236" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R236" s="13" t="s">
-        <v>598</v>
+      <c r="Q236" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R236" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S236" s="12" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="4" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>16</v>
@@ -17782,10 +17806,10 @@
         <v>42</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>45</v>
@@ -17820,19 +17844,19 @@
         <f aca="false">IF(O237&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q237" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R237" s="13" t="s">
-        <v>598</v>
+      <c r="Q237" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R237" s="4" t="s">
+        <v>621</v>
       </c>
       <c r="S237" s="12" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="4" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>16</v>
@@ -17844,10 +17868,10 @@
         <v>42</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>45</v>
@@ -17882,19 +17906,19 @@
         <f aca="false">IF(O238&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q238" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R238" s="13" t="s">
-        <v>598</v>
+      <c r="Q238" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R238" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="S238" s="12" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>16</v>
@@ -17906,10 +17930,10 @@
         <v>42</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>45</v>
@@ -17944,19 +17968,19 @@
         <f aca="false">IF(O239&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q239" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R239" s="13" t="s">
-        <v>598</v>
+      <c r="Q239" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R239" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="S239" s="12" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="4" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>16</v>
@@ -17968,10 +17992,10 @@
         <v>42</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>45</v>
@@ -18006,19 +18030,19 @@
         <f aca="false">IF(O240&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q240" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R240" s="13" t="s">
-        <v>598</v>
+      <c r="Q240" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R240" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S240" s="12" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="4" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>16</v>
@@ -18030,10 +18054,10 @@
         <v>42</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>45</v>
@@ -18068,19 +18092,19 @@
         <f aca="false">IF(O241&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q241" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R241" s="13" t="s">
-        <v>598</v>
+      <c r="Q241" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R241" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S241" s="12" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="4" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>16</v>
@@ -18092,10 +18116,10 @@
         <v>42</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>45</v>
@@ -18130,19 +18154,19 @@
         <f aca="false">IF(O242&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q242" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R242" s="13" t="s">
-        <v>598</v>
+      <c r="Q242" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R242" s="4" t="s">
+        <v>613</v>
       </c>
       <c r="S242" s="12" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="4" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>16</v>
@@ -18154,10 +18178,10 @@
         <v>42</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>45</v>
@@ -18192,19 +18216,19 @@
         <f aca="false">IF(O243&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q243" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R243" s="13" t="s">
-        <v>598</v>
+      <c r="Q243" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R243" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S243" s="12" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="4" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>16</v>
@@ -18216,10 +18240,10 @@
         <v>42</v>
       </c>
       <c r="E244" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="F244" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="F244" s="4" t="s">
-        <v>648</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>45</v>
@@ -18254,19 +18278,19 @@
         <f aca="false">IF(O244&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q244" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R244" s="13" t="s">
-        <v>598</v>
+      <c r="Q244" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R244" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S244" s="12" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="4" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>16</v>
@@ -18278,10 +18302,10 @@
         <v>42</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>45</v>
@@ -18316,19 +18340,19 @@
         <f aca="false">IF(O245&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q245" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R245" s="13" t="s">
-        <v>598</v>
+      <c r="Q245" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R245" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S245" s="12" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="4" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>16</v>
@@ -18343,7 +18367,7 @@
         <v>552</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>45</v>
@@ -18378,19 +18402,19 @@
         <f aca="false">IF(O246&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q246" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R246" s="13" t="s">
-        <v>598</v>
+      <c r="Q246" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R246" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S246" s="12" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="4" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>16</v>
@@ -18405,7 +18429,7 @@
         <v>552</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>45</v>
@@ -18440,19 +18464,19 @@
         <f aca="false">IF(O247&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q247" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R247" s="13" t="s">
-        <v>598</v>
+      <c r="Q247" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R247" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S247" s="12" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="4" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>16</v>
@@ -18467,7 +18491,7 @@
         <v>552</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>45</v>
@@ -18502,19 +18526,19 @@
         <f aca="false">IF(O248&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q248" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R248" s="13" t="s">
-        <v>598</v>
+      <c r="Q248" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R248" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="S248" s="12" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B249" s="4" t="s">
         <v>16</v>
@@ -18526,10 +18550,10 @@
         <v>42</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="G249" s="4" t="s">
         <v>45</v>
@@ -18564,19 +18588,19 @@
         <f aca="false">IF(O249&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q249" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R249" s="13" t="s">
+      <c r="Q249" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R249" s="4" t="s">
         <v>598</v>
       </c>
       <c r="S249" s="12" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>16</v>
@@ -18588,10 +18612,10 @@
         <v>42</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>45</v>
@@ -18626,19 +18650,19 @@
         <f aca="false">IF(O250&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q250" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R250" s="13" t="s">
+      <c r="Q250" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R250" s="4" t="s">
         <v>598</v>
       </c>
       <c r="S250" s="12" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="4" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="B251" s="4" t="s">
         <v>16</v>
@@ -18650,10 +18674,10 @@
         <v>42</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>45</v>
@@ -18688,19 +18712,19 @@
         <f aca="false">IF(O251&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q251" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R251" s="13" t="s">
+      <c r="Q251" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R251" s="4" t="s">
         <v>598</v>
       </c>
       <c r="S251" s="12" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="4" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>16</v>
@@ -18712,10 +18736,10 @@
         <v>42</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>45</v>
@@ -18750,19 +18774,19 @@
         <f aca="false">IF(O252&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q252" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R252" s="13" t="s">
-        <v>598</v>
+      <c r="Q252" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R252" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S252" s="12" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B253" s="4" t="s">
         <v>16</v>
@@ -18774,10 +18798,10 @@
         <v>42</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>45</v>
@@ -18812,19 +18836,19 @@
         <f aca="false">IF(O253&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q253" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R253" s="13" t="s">
-        <v>598</v>
+      <c r="Q253" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R253" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S253" s="12" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="4" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="B254" s="4" t="s">
         <v>16</v>
@@ -18836,10 +18860,10 @@
         <v>91</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G254" s="4" t="s">
         <v>45</v>
@@ -18874,19 +18898,19 @@
         <f aca="false">IF(O254&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q254" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R254" s="13" t="s">
-        <v>598</v>
+      <c r="Q254" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R254" s="4" t="s">
+        <v>685</v>
       </c>
       <c r="S254" s="12" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="4" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="B255" s="4" t="s">
         <v>16</v>
@@ -18898,10 +18922,10 @@
         <v>91</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>45</v>
@@ -18936,19 +18960,19 @@
         <f aca="false">IF(O255&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q255" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R255" s="13" t="s">
-        <v>598</v>
+      <c r="Q255" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R255" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S255" s="12" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="4" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="B256" s="4" t="s">
         <v>16</v>
@@ -18960,10 +18984,10 @@
         <v>91</v>
       </c>
       <c r="E256" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>45</v>
@@ -18998,19 +19022,19 @@
         <f aca="false">IF(O256&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q256" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R256" s="13" t="s">
-        <v>598</v>
+      <c r="Q256" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R256" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S256" s="12" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="4" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>16</v>
@@ -19022,10 +19046,10 @@
         <v>91</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>45</v>
@@ -19060,19 +19084,19 @@
         <f aca="false">IF(O257&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q257" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R257" s="13" t="s">
-        <v>598</v>
+      <c r="Q257" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R257" s="4" t="s">
+        <v>685</v>
       </c>
       <c r="S257" s="12" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="4" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>16</v>
@@ -19084,10 +19108,10 @@
         <v>91</v>
       </c>
       <c r="E258" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>45</v>
@@ -19122,19 +19146,19 @@
         <f aca="false">IF(O258&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q258" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R258" s="13" t="s">
-        <v>598</v>
+      <c r="Q258" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R258" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S258" s="12" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="4" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>16</v>
@@ -19146,10 +19170,10 @@
         <v>91</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G259" s="4" t="s">
         <v>45</v>
@@ -19184,19 +19208,19 @@
         <f aca="false">IF(O259&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q259" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R259" s="13" t="s">
-        <v>598</v>
+      <c r="Q259" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R259" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S259" s="12" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="4" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B260" s="4" t="s">
         <v>16</v>
@@ -19208,10 +19232,10 @@
         <v>91</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>45</v>
@@ -19246,19 +19270,19 @@
         <f aca="false">IF(O260&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q260" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R260" s="13" t="s">
-        <v>598</v>
+      <c r="Q260" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R260" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S260" s="12" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="4" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B261" s="4" t="s">
         <v>16</v>
@@ -19270,10 +19294,10 @@
         <v>91</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>45</v>
@@ -19308,19 +19332,19 @@
         <f aca="false">IF(O261&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q261" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R261" s="13" t="s">
-        <v>598</v>
+      <c r="Q261" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R261" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="S261" s="12" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="4" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="B262" s="4" t="s">
         <v>16</v>
@@ -19332,10 +19356,10 @@
         <v>91</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G262" s="4" t="s">
         <v>45</v>
@@ -19370,19 +19394,19 @@
         <f aca="false">IF(O262&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q262" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R262" s="13" t="s">
-        <v>598</v>
+      <c r="Q262" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R262" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S262" s="12" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="4" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B263" s="4" t="s">
         <v>16</v>
@@ -19394,10 +19418,10 @@
         <v>91</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>45</v>
@@ -19432,19 +19456,19 @@
         <f aca="false">IF(O263&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>NON</v>
       </c>
-      <c r="Q263" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R263" s="13" t="s">
-        <v>598</v>
+      <c r="Q263" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R263" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S263" s="12" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="B264" s="4" t="s">
         <v>16</v>
@@ -19456,10 +19480,10 @@
         <v>91</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>45</v>
@@ -19494,19 +19518,19 @@
         <f aca="false">IF(O264&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q264" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R264" s="13" t="s">
-        <v>598</v>
+      <c r="Q264" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R264" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S264" s="12" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="4" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B265" s="4" t="s">
         <v>16</v>
@@ -19518,10 +19542,10 @@
         <v>91</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>45</v>
@@ -19556,19 +19580,19 @@
         <f aca="false">IF(O265&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q265" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R265" s="13" t="s">
-        <v>598</v>
+      <c r="Q265" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R265" s="4" t="s">
+        <v>613</v>
       </c>
       <c r="S265" s="12" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="4" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="B266" s="4" t="s">
         <v>16</v>
@@ -19580,10 +19604,10 @@
         <v>91</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G266" s="4" t="s">
         <v>45</v>
@@ -19618,19 +19642,19 @@
         <f aca="false">IF(O266&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q266" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R266" s="13" t="s">
-        <v>598</v>
+      <c r="Q266" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R266" s="4" t="s">
+        <v>613</v>
       </c>
       <c r="S266" s="12" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="4" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="B267" s="4" t="s">
         <v>16</v>
@@ -19642,10 +19666,10 @@
         <v>91</v>
       </c>
       <c r="E267" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>45</v>
@@ -19680,19 +19704,19 @@
         <f aca="false">IF(O267&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q267" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R267" s="13" t="s">
-        <v>598</v>
+      <c r="Q267" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R267" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S267" s="12" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="4" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="B268" s="4" t="s">
         <v>16</v>
@@ -19704,10 +19728,10 @@
         <v>91</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>45</v>
@@ -19742,19 +19766,19 @@
         <f aca="false">IF(O268&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q268" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R268" s="13" t="s">
-        <v>598</v>
+      <c r="Q268" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R268" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="S268" s="12" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="4" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="B269" s="4" t="s">
         <v>16</v>
@@ -19766,10 +19790,10 @@
         <v>91</v>
       </c>
       <c r="E269" s="4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G269" s="4" t="s">
         <v>45</v>
@@ -19804,19 +19828,19 @@
         <f aca="false">IF(O269&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q269" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R269" s="13" t="s">
-        <v>598</v>
+      <c r="Q269" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R269" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S269" s="12" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="4" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="B270" s="4" t="s">
         <v>16</v>
@@ -19828,10 +19852,10 @@
         <v>91</v>
       </c>
       <c r="E270" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G270" s="4" t="s">
         <v>45</v>
@@ -19866,19 +19890,19 @@
         <f aca="false">IF(O270&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q270" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R270" s="13" t="s">
-        <v>598</v>
+      <c r="Q270" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R270" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="S270" s="12" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="4" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B271" s="4" t="s">
         <v>16</v>
@@ -19890,10 +19914,10 @@
         <v>91</v>
       </c>
       <c r="E271" s="4" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G271" s="4" t="s">
         <v>45</v>
@@ -19928,14 +19952,14 @@
         <f aca="false">IF(O271&lt;=Hypothèses!$B$3,"oui","NON")</f>
         <v>oui</v>
       </c>
-      <c r="Q271" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="R271" s="13" t="s">
-        <v>598</v>
+      <c r="Q271" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R271" s="4" t="s">
+        <v>717</v>
       </c>
       <c r="S271" s="12" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -19985,40 +20009,40 @@
         <v>27</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20035,10 +20059,10 @@
         <v>279</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G2" s="9" t="n">
         <v>90</v>
@@ -20087,10 +20111,10 @@
         <v>279</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G3" s="9" t="n">
         <v>90</v>
@@ -20139,10 +20163,10 @@
         <v>279</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G4" s="9" t="n">
         <v>90</v>
@@ -20191,10 +20215,10 @@
         <v>279</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>90</v>
@@ -20243,10 +20267,10 @@
         <v>135</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>90</v>
@@ -20295,10 +20319,10 @@
         <v>135</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>90</v>
@@ -20347,10 +20371,10 @@
         <v>135</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>90</v>
@@ -20399,10 +20423,10 @@
         <v>135</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>90</v>
@@ -20451,10 +20475,10 @@
         <v>135</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>90</v>
@@ -20503,10 +20527,10 @@
         <v>135</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>90</v>
@@ -20555,10 +20579,10 @@
         <v>143</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>90</v>
@@ -20607,10 +20631,10 @@
         <v>143</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>90</v>
@@ -20659,10 +20683,10 @@
         <v>143</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>90</v>
@@ -20711,10 +20735,10 @@
         <v>143</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>90</v>
@@ -20763,10 +20787,10 @@
         <v>143</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>90</v>
@@ -20815,10 +20839,10 @@
         <v>143</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>90</v>
@@ -20867,10 +20891,10 @@
         <v>143</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>90</v>
@@ -20919,10 +20943,10 @@
         <v>143</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>90</v>
@@ -20971,10 +20995,10 @@
         <v>143</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>90</v>
@@ -21023,10 +21047,10 @@
         <v>143</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>90</v>
@@ -21075,10 +21099,10 @@
         <v>143</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>90</v>
@@ -21127,10 +21151,10 @@
         <v>143</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>90</v>
@@ -21179,10 +21203,10 @@
         <v>143</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>90</v>
@@ -21231,10 +21255,10 @@
         <v>143</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>90</v>
@@ -21283,10 +21307,10 @@
         <v>143</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>90</v>
@@ -21335,10 +21359,10 @@
         <v>143</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>90</v>
@@ -21387,10 +21411,10 @@
         <v>143</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>90</v>
@@ -21439,10 +21463,10 @@
         <v>143</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>90</v>
@@ -21491,10 +21515,10 @@
         <v>44</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
@@ -21543,10 +21567,10 @@
         <v>44</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
@@ -21595,10 +21619,10 @@
         <v>44</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
@@ -21647,10 +21671,10 @@
         <v>44</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0</v>
@@ -21699,10 +21723,10 @@
         <v>44</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
@@ -21751,10 +21775,10 @@
         <v>44</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0</v>
@@ -21803,10 +21827,10 @@
         <v>44</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
@@ -21855,10 +21879,10 @@
         <v>44</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
@@ -21907,10 +21931,10 @@
         <v>44</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0</v>
@@ -21959,10 +21983,10 @@
         <v>44</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
@@ -22011,10 +22035,10 @@
         <v>44</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0</v>
@@ -22063,10 +22087,10 @@
         <v>44</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
@@ -22115,10 +22139,10 @@
         <v>44</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0</v>
@@ -22167,10 +22191,10 @@
         <v>44</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>0</v>
@@ -22219,10 +22243,10 @@
         <v>44</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0</v>
@@ -22271,10 +22295,10 @@
         <v>44</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0</v>
@@ -22323,10 +22347,10 @@
         <v>44</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
@@ -22375,10 +22399,10 @@
         <v>44</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
@@ -22427,10 +22451,10 @@
         <v>44</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
@@ -22479,10 +22503,10 @@
         <v>44</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
@@ -22531,10 +22555,10 @@
         <v>44</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0</v>
@@ -22583,10 +22607,10 @@
         <v>44</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0</v>
@@ -22635,10 +22659,10 @@
         <v>44</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>0</v>
@@ -22687,10 +22711,10 @@
         <v>44</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
@@ -22739,10 +22763,10 @@
         <v>44</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>0</v>
@@ -22791,10 +22815,10 @@
         <v>44</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0</v>
@@ -22843,10 +22867,10 @@
         <v>44</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>0</v>
@@ -22895,10 +22919,10 @@
         <v>44</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>0</v>
@@ -22947,10 +22971,10 @@
         <v>279</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>90</v>
@@ -22999,10 +23023,10 @@
         <v>279</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>90</v>
@@ -23051,10 +23075,10 @@
         <v>279</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>90</v>
@@ -23103,10 +23127,10 @@
         <v>279</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>90</v>
@@ -23155,10 +23179,10 @@
         <v>135</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>90</v>
@@ -23207,10 +23231,10 @@
         <v>135</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>90</v>
@@ -23259,10 +23283,10 @@
         <v>135</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>90</v>
@@ -23311,10 +23335,10 @@
         <v>135</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>90</v>
@@ -23363,10 +23387,10 @@
         <v>135</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>90</v>
@@ -23415,10 +23439,10 @@
         <v>143</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>90</v>
@@ -23467,10 +23491,10 @@
         <v>143</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>90</v>
@@ -23519,10 +23543,10 @@
         <v>143</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>90</v>
@@ -23571,10 +23595,10 @@
         <v>143</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>90</v>
@@ -23623,10 +23647,10 @@
         <v>143</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>90</v>
@@ -23675,10 +23699,10 @@
         <v>143</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>90</v>
@@ -23727,10 +23751,10 @@
         <v>143</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>90</v>
@@ -23779,10 +23803,10 @@
         <v>143</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>90</v>
@@ -23831,10 +23855,10 @@
         <v>143</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>90</v>
@@ -23883,10 +23907,10 @@
         <v>143</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>90</v>
@@ -23935,10 +23959,10 @@
         <v>143</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>90</v>
@@ -23987,10 +24011,10 @@
         <v>143</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>90</v>
@@ -24039,10 +24063,10 @@
         <v>143</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>90</v>
@@ -24091,10 +24115,10 @@
         <v>143</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>90</v>
@@ -24143,10 +24167,10 @@
         <v>143</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>90</v>
@@ -24195,10 +24219,10 @@
         <v>143</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>90</v>
@@ -24247,10 +24271,10 @@
         <v>143</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>90</v>
@@ -24299,10 +24323,10 @@
         <v>143</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>90</v>
@@ -24351,10 +24375,10 @@
         <v>44</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
@@ -24403,10 +24427,10 @@
         <v>44</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>0</v>
@@ -24455,10 +24479,10 @@
         <v>44</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>0</v>
@@ -24507,10 +24531,10 @@
         <v>44</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>0</v>
@@ -24559,10 +24583,10 @@
         <v>44</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>0</v>
@@ -24611,10 +24635,10 @@
         <v>44</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>0</v>
@@ -24663,10 +24687,10 @@
         <v>44</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>0</v>
@@ -24715,10 +24739,10 @@
         <v>44</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>0</v>
@@ -24767,10 +24791,10 @@
         <v>44</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
@@ -24819,10 +24843,10 @@
         <v>44</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>0</v>
@@ -24871,10 +24895,10 @@
         <v>44</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>0</v>
@@ -24923,10 +24947,10 @@
         <v>44</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>0</v>
@@ -24975,10 +24999,10 @@
         <v>44</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>0</v>
@@ -25027,10 +25051,10 @@
         <v>44</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>0</v>
@@ -25079,10 +25103,10 @@
         <v>44</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>0</v>
@@ -25131,10 +25155,10 @@
         <v>44</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>0</v>
@@ -25183,10 +25207,10 @@
         <v>44</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>0</v>
@@ -25235,10 +25259,10 @@
         <v>44</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>0</v>
@@ -25287,10 +25311,10 @@
         <v>44</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>0</v>
@@ -25339,10 +25363,10 @@
         <v>44</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G104" s="9" t="n">
         <v>0</v>
@@ -25391,10 +25415,10 @@
         <v>44</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G105" s="9" t="n">
         <v>0</v>
@@ -25443,10 +25467,10 @@
         <v>44</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>0</v>
@@ -25495,10 +25519,10 @@
         <v>44</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>0</v>
@@ -25547,10 +25571,10 @@
         <v>44</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>0</v>
@@ -25581,7 +25605,7 @@
         <v>oui</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P108" s="4" t="s">
         <v>273</v>
@@ -25601,10 +25625,10 @@
         <v>44</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
@@ -25653,10 +25677,10 @@
         <v>44</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>0</v>
@@ -25705,10 +25729,10 @@
         <v>44</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>0</v>
@@ -25757,10 +25781,10 @@
         <v>143</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>90</v>
@@ -25809,10 +25833,10 @@
         <v>143</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>90</v>
@@ -25861,10 +25885,10 @@
         <v>143</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G114" s="9" t="n">
         <v>90</v>
@@ -25913,10 +25937,10 @@
         <v>143</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G115" s="9" t="n">
         <v>90</v>
@@ -25965,10 +25989,10 @@
         <v>143</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>90</v>
@@ -26017,10 +26041,10 @@
         <v>143</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>90</v>
@@ -26069,10 +26093,10 @@
         <v>143</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G118" s="9" t="n">
         <v>90</v>
@@ -26121,10 +26145,10 @@
         <v>143</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G119" s="9" t="n">
         <v>90</v>
@@ -26173,10 +26197,10 @@
         <v>143</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G120" s="9" t="n">
         <v>90</v>
@@ -26225,10 +26249,10 @@
         <v>143</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>90</v>
@@ -26277,10 +26301,10 @@
         <v>143</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>90</v>
@@ -26329,10 +26353,10 @@
         <v>143</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>90</v>
@@ -26381,10 +26405,10 @@
         <v>143</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>90</v>
@@ -26433,10 +26457,10 @@
         <v>143</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G125" s="9" t="n">
         <v>90</v>
@@ -26485,10 +26509,10 @@
         <v>143</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>90</v>
@@ -26537,10 +26561,10 @@
         <v>143</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G127" s="9" t="n">
         <v>90</v>
@@ -26589,10 +26613,10 @@
         <v>143</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G128" s="9" t="n">
         <v>90</v>
@@ -26641,10 +26665,10 @@
         <v>143</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G129" s="9" t="n">
         <v>90</v>
@@ -26693,10 +26717,10 @@
         <v>143</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G130" s="9" t="n">
         <v>90</v>
@@ -26745,10 +26769,10 @@
         <v>143</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G131" s="9" t="n">
         <v>90</v>
@@ -26797,10 +26821,10 @@
         <v>143</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>90</v>
@@ -26849,10 +26873,10 @@
         <v>143</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G133" s="9" t="n">
         <v>90</v>
@@ -26901,10 +26925,10 @@
         <v>143</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G134" s="9" t="n">
         <v>90</v>
@@ -26953,10 +26977,10 @@
         <v>143</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G135" s="9" t="n">
         <v>90</v>
@@ -27005,10 +27029,10 @@
         <v>143</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G136" s="9" t="n">
         <v>90</v>
@@ -27039,7 +27063,7 @@
         <v>oui</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P136" s="4" t="s">
         <v>397</v>
@@ -27059,10 +27083,10 @@
         <v>143</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G137" s="9" t="n">
         <v>90</v>
@@ -27111,10 +27135,10 @@
         <v>44</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G138" s="9" t="n">
         <v>0</v>
@@ -27163,10 +27187,10 @@
         <v>44</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G139" s="9" t="n">
         <v>0</v>
@@ -27215,10 +27239,10 @@
         <v>44</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G140" s="9" t="n">
         <v>0</v>
@@ -27267,10 +27291,10 @@
         <v>44</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>0</v>
@@ -27319,10 +27343,10 @@
         <v>44</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>0</v>
@@ -27371,10 +27395,10 @@
         <v>44</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>0</v>
@@ -27423,10 +27447,10 @@
         <v>44</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>0</v>
@@ -27475,10 +27499,10 @@
         <v>44</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>0</v>
@@ -27527,10 +27551,10 @@
         <v>44</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>0</v>
@@ -27579,10 +27603,10 @@
         <v>44</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G147" s="9" t="n">
         <v>0</v>
@@ -27631,10 +27655,10 @@
         <v>44</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>0</v>
@@ -27683,10 +27707,10 @@
         <v>44</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G149" s="9" t="n">
         <v>0</v>
@@ -27735,10 +27759,10 @@
         <v>44</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G150" s="9" t="n">
         <v>0</v>
@@ -27787,10 +27811,10 @@
         <v>44</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G151" s="9" t="n">
         <v>0</v>
@@ -27839,10 +27863,10 @@
         <v>44</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G152" s="9" t="n">
         <v>0</v>
@@ -27891,10 +27915,10 @@
         <v>44</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G153" s="9" t="n">
         <v>0</v>
@@ -27943,10 +27967,10 @@
         <v>44</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>0</v>
@@ -27977,7 +28001,7 @@
         <v>oui</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P154" s="4" t="s">
         <v>435</v>
@@ -27997,10 +28021,10 @@
         <v>44</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>0</v>
@@ -28049,10 +28073,10 @@
         <v>44</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>0</v>
@@ -28101,10 +28125,10 @@
         <v>44</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>0</v>
@@ -28153,10 +28177,10 @@
         <v>44</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>0</v>
@@ -28205,10 +28229,10 @@
         <v>44</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>0</v>
@@ -28257,10 +28281,10 @@
         <v>44</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>0</v>
@@ -28309,10 +28333,10 @@
         <v>44</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>0</v>
@@ -28361,10 +28385,10 @@
         <v>44</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>0</v>
@@ -28413,10 +28437,10 @@
         <v>44</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>0</v>
@@ -28465,10 +28489,10 @@
         <v>467</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>50</v>
@@ -28499,10 +28523,10 @@
         <v>oui</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P164" s="4" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28519,10 +28543,10 @@
         <v>474</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G165" s="9" t="n">
         <v>90</v>
@@ -28553,10 +28577,10 @@
         <v>oui</v>
       </c>
       <c r="O165" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P165" s="4" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28573,10 +28597,10 @@
         <v>478</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G166" s="9" t="n">
         <v>72</v>
@@ -28607,30 +28631,30 @@
         <v>oui</v>
       </c>
       <c r="O166" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P166" s="4" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D167" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="F167" s="4" t="s">
         <v>736</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>728</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>2</v>
@@ -28661,7 +28685,7 @@
         <v>oui</v>
       </c>
       <c r="O167" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P167" s="4"/>
     </row>
@@ -28679,10 +28703,10 @@
         <v>482</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>75</v>
@@ -28713,10 +28737,10 @@
         <v>oui</v>
       </c>
       <c r="O168" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P168" s="4" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28733,10 +28757,10 @@
         <v>486</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>50</v>
@@ -28767,10 +28791,10 @@
         <v>oui</v>
       </c>
       <c r="O169" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P169" s="4" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28787,10 +28811,10 @@
         <v>489</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>50</v>
@@ -28821,10 +28845,10 @@
         <v>oui</v>
       </c>
       <c r="O170" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P170" s="4" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28841,10 +28865,10 @@
         <v>492</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>75</v>
@@ -28876,27 +28900,27 @@
       </c>
       <c r="O171" s="4"/>
       <c r="P171" s="4" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>2</v>
@@ -28927,28 +28951,28 @@
         <v>oui</v>
       </c>
       <c r="O172" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P172" s="4"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>3</v>
@@ -28979,7 +29003,7 @@
         <v>oui</v>
       </c>
       <c r="O173" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P173" s="4"/>
     </row>
@@ -28997,10 +29021,10 @@
         <v>496</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>126</v>
@@ -29031,10 +29055,10 @@
         <v>oui</v>
       </c>
       <c r="O174" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P174" s="4" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29051,10 +29075,10 @@
         <v>500</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>108</v>
@@ -29086,27 +29110,27 @@
       </c>
       <c r="O175" s="4"/>
       <c r="P175" s="4" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>4</v>
@@ -29137,7 +29161,7 @@
         <v>oui</v>
       </c>
       <c r="O176" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P176" s="4"/>
     </row>
@@ -29155,10 +29179,10 @@
         <v>504</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>234</v>
@@ -29189,30 +29213,30 @@
         <v>oui</v>
       </c>
       <c r="O177" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P177" s="4" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>5</v>
@@ -29243,28 +29267,28 @@
         <v>oui</v>
       </c>
       <c r="O178" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P178" s="4"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>3</v>
@@ -29295,28 +29319,28 @@
         <v>oui</v>
       </c>
       <c r="O179" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P179" s="4"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>5</v>
@@ -29347,7 +29371,7 @@
         <v>oui</v>
       </c>
       <c r="O180" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P180" s="4"/>
     </row>
@@ -29365,10 +29389,10 @@
         <v>508</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G181" s="9" t="n">
         <v>50</v>
@@ -29399,10 +29423,10 @@
         <v>oui</v>
       </c>
       <c r="O181" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P181" s="4" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29419,10 +29443,10 @@
         <v>511</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G182" s="9" t="n">
         <v>75</v>
@@ -29454,7 +29478,7 @@
       </c>
       <c r="O182" s="4"/>
       <c r="P182" s="4" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29471,10 +29495,10 @@
         <v>515</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G183" s="9" t="n">
         <v>75</v>
@@ -29506,27 +29530,27 @@
       </c>
       <c r="O183" s="4"/>
       <c r="P183" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G184" s="9" t="n">
         <v>4</v>
@@ -29557,28 +29581,28 @@
         <v>oui</v>
       </c>
       <c r="O184" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P184" s="4"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>6</v>
@@ -29609,7 +29633,7 @@
         <v>oui</v>
       </c>
       <c r="O185" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P185" s="4"/>
     </row>
@@ -29627,10 +29651,10 @@
         <v>519</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>234</v>
@@ -29661,10 +29685,10 @@
         <v>oui</v>
       </c>
       <c r="O186" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P186" s="4" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29681,10 +29705,10 @@
         <v>523</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>2486</v>
@@ -29715,10 +29739,10 @@
         <v>oui</v>
       </c>
       <c r="O187" s="4" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="P187" s="4" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29735,10 +29759,10 @@
         <v>533</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>75</v>
@@ -29770,27 +29794,27 @@
       </c>
       <c r="O188" s="4"/>
       <c r="P188" s="4" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>2</v>
@@ -29821,28 +29845,28 @@
         <v>oui</v>
       </c>
       <c r="O189" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P189" s="4"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>2</v>
@@ -29873,28 +29897,28 @@
         <v>oui</v>
       </c>
       <c r="O190" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P190" s="4"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>5</v>
@@ -29925,28 +29949,28 @@
         <v>oui</v>
       </c>
       <c r="O191" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P191" s="4"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>21</v>
@@ -29977,7 +30001,7 @@
         <v>oui</v>
       </c>
       <c r="O192" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P192" s="4"/>
     </row>
@@ -29995,10 +30019,10 @@
         <v>537</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>100</v>
@@ -30030,27 +30054,27 @@
       </c>
       <c r="O193" s="4"/>
       <c r="P193" s="4" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>4</v>
@@ -30081,28 +30105,28 @@
         <v>oui</v>
       </c>
       <c r="O194" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P194" s="4"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D195" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="F195" s="4" t="s">
         <v>736</v>
-      </c>
-      <c r="E195" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="F195" s="4" t="s">
-        <v>728</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>2</v>
@@ -30133,7 +30157,7 @@
         <v>oui</v>
       </c>
       <c r="O195" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P195" s="4"/>
     </row>
@@ -30151,10 +30175,10 @@
         <v>541</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>25</v>
@@ -30186,27 +30210,27 @@
       </c>
       <c r="O196" s="4"/>
       <c r="P196" s="4" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>2</v>
@@ -30237,7 +30261,7 @@
         <v>oui</v>
       </c>
       <c r="O197" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P197" s="4"/>
     </row>
@@ -30255,10 +30279,10 @@
         <v>545</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>108</v>
@@ -30289,30 +30313,30 @@
         <v>oui</v>
       </c>
       <c r="O198" s="4" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="P198" s="4" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>2</v>
@@ -30343,28 +30367,28 @@
         <v>oui</v>
       </c>
       <c r="O199" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P199" s="4"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>3</v>
@@ -30395,28 +30419,28 @@
         <v>oui</v>
       </c>
       <c r="O200" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P200" s="4"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>2</v>
@@ -30447,28 +30471,28 @@
         <v>oui</v>
       </c>
       <c r="O201" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P201" s="4"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>6</v>
@@ -30499,28 +30523,28 @@
         <v>oui</v>
       </c>
       <c r="O202" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P202" s="4"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="4" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>8</v>
@@ -30551,28 +30575,28 @@
         <v>oui</v>
       </c>
       <c r="O203" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P203" s="4"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>2</v>
@@ -30603,7 +30627,7 @@
         <v>oui</v>
       </c>
       <c r="O204" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="P204" s="4"/>
     </row>
@@ -30621,10 +30645,10 @@
         <v>523</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>440</v>
@@ -30655,10 +30679,10 @@
         <v>oui</v>
       </c>
       <c r="O205" s="4" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="P205" s="4" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30675,10 +30699,10 @@
         <v>553</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>726</v>
@@ -30709,10 +30733,10 @@
         <v>oui</v>
       </c>
       <c r="O206" s="4" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="P206" s="4" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30729,10 +30753,10 @@
         <v>553</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>704</v>
@@ -30763,10 +30787,10 @@
         <v>oui</v>
       </c>
       <c r="O207" s="4" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="P207" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30783,10 +30807,10 @@
         <v>595</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>0</v>
@@ -30817,7 +30841,7 @@
         <v>oui</v>
       </c>
       <c r="O208" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P208" s="4" t="s">
         <v>593</v>
@@ -30825,7 +30849,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>42</v>
@@ -30837,10 +30861,10 @@
         <v>601</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>0</v>
@@ -30871,7 +30895,7 @@
         <v>oui</v>
       </c>
       <c r="O209" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P209" s="4" t="s">
         <v>600</v>
@@ -30879,22 +30903,22 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>0</v>
@@ -30925,30 +30949,30 @@
         <v>oui</v>
       </c>
       <c r="O210" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P210" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>0</v>
@@ -30979,30 +31003,30 @@
         <v>oui</v>
       </c>
       <c r="O211" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P211" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>0</v>
@@ -31033,30 +31057,30 @@
         <v>oui</v>
       </c>
       <c r="O212" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P212" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="4" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>0</v>
@@ -31087,30 +31111,30 @@
         <v>oui</v>
       </c>
       <c r="O213" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P213" s="4" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="4" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>0</v>
@@ -31141,30 +31165,30 @@
         <v>oui</v>
       </c>
       <c r="O214" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P214" s="4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>0</v>
@@ -31195,30 +31219,30 @@
         <v>oui</v>
       </c>
       <c r="O215" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P215" s="4" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>0</v>
@@ -31249,30 +31273,30 @@
         <v>oui</v>
       </c>
       <c r="O216" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P216" s="4" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>0</v>
@@ -31303,30 +31327,30 @@
         <v>oui</v>
       </c>
       <c r="O217" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P217" s="4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="4" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>0</v>
@@ -31357,30 +31381,30 @@
         <v>oui</v>
       </c>
       <c r="O218" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P218" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>0</v>
@@ -31411,30 +31435,30 @@
         <v>oui</v>
       </c>
       <c r="O219" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P219" s="4" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="4" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>0</v>
@@ -31465,30 +31489,30 @@
         <v>oui</v>
       </c>
       <c r="O220" s="4" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="P220" s="4" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G221" s="9" t="n">
         <v>0</v>
@@ -31519,30 +31543,30 @@
         <v>oui</v>
       </c>
       <c r="O221" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P221" s="4" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="4" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C222" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D222" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="D222" s="4" t="s">
-        <v>648</v>
-      </c>
       <c r="E222" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G222" s="9" t="n">
         <v>0</v>
@@ -31573,30 +31597,30 @@
         <v>oui</v>
       </c>
       <c r="O222" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P222" s="4" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>0</v>
@@ -31627,30 +31651,30 @@
         <v>oui</v>
       </c>
       <c r="O223" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P223" s="4" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G224" s="9" t="n">
         <v>0</v>
@@ -31681,30 +31705,30 @@
         <v>oui</v>
       </c>
       <c r="O224" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P224" s="4" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>0</v>
@@ -31735,15 +31759,15 @@
         <v>oui</v>
       </c>
       <c r="O225" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P225" s="4" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>42</v>
@@ -31752,13 +31776,13 @@
         <v>552</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>0</v>
@@ -31789,30 +31813,30 @@
         <v>oui</v>
       </c>
       <c r="O226" s="4" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="P226" s="4" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G227" s="9" t="n">
         <v>0</v>
@@ -31843,30 +31867,30 @@
         <v>oui</v>
       </c>
       <c r="O227" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P227" s="4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G228" s="9" t="n">
         <v>0</v>
@@ -31897,30 +31921,30 @@
         <v>oui</v>
       </c>
       <c r="O228" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P228" s="4" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G229" s="9" t="n">
         <v>0</v>
@@ -31951,30 +31975,30 @@
         <v>oui</v>
       </c>
       <c r="O229" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P229" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G230" s="9" t="n">
         <v>0</v>
@@ -32005,30 +32029,30 @@
         <v>oui</v>
       </c>
       <c r="O230" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P230" s="4" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B231" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G231" s="9" t="n">
         <v>0</v>
@@ -32059,30 +32083,30 @@
         <v>oui</v>
       </c>
       <c r="O231" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P231" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="B232" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G232" s="9" t="n">
         <v>0</v>
@@ -32113,30 +32137,30 @@
         <v>oui</v>
       </c>
       <c r="O232" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P232" s="4" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B233" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G233" s="9" t="n">
         <v>0</v>
@@ -32167,30 +32191,30 @@
         <v>oui</v>
       </c>
       <c r="O233" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P233" s="4" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="B234" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G234" s="9" t="n">
         <v>0</v>
@@ -32221,30 +32245,30 @@
         <v>oui</v>
       </c>
       <c r="O234" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P234" s="4" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G235" s="9" t="n">
         <v>0</v>
@@ -32275,30 +32299,30 @@
         <v>oui</v>
       </c>
       <c r="O235" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P235" s="4" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="4" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="B236" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G236" s="9" t="n">
         <v>0</v>
@@ -32329,30 +32353,30 @@
         <v>oui</v>
       </c>
       <c r="O236" s="4" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="P236" s="4" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="4" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="B237" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G237" s="9" t="n">
         <v>0</v>
@@ -32383,30 +32407,30 @@
         <v>oui</v>
       </c>
       <c r="O237" s="4" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="P237" s="4" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="4" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="B238" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G238" s="9" t="n">
         <v>0</v>
@@ -32437,30 +32461,30 @@
         <v>oui</v>
       </c>
       <c r="O238" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P238" s="4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="B239" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G239" s="9" t="n">
         <v>0</v>
@@ -32491,30 +32515,30 @@
         <v>oui</v>
       </c>
       <c r="O239" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P239" s="4" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="4" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="B240" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G240" s="9" t="n">
         <v>0</v>
@@ -32545,30 +32569,30 @@
         <v>oui</v>
       </c>
       <c r="O240" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P240" s="4" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="4" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B241" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G241" s="9" t="n">
         <v>0</v>
@@ -32599,30 +32623,30 @@
         <v>oui</v>
       </c>
       <c r="O241" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P241" s="4" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="4" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G242" s="9" t="n">
         <v>0</v>
@@ -32653,30 +32677,30 @@
         <v>oui</v>
       </c>
       <c r="O242" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P242" s="4" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="4" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G243" s="9" t="n">
         <v>0</v>
@@ -32707,30 +32731,30 @@
         <v>oui</v>
       </c>
       <c r="O243" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P243" s="4" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="4" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B244" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E244" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G244" s="9" t="n">
         <v>0</v>
@@ -32761,30 +32785,30 @@
         <v>oui</v>
       </c>
       <c r="O244" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P244" s="4" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="4" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="G245" s="9" t="n">
         <v>0</v>
@@ -32815,10 +32839,10 @@
         <v>oui</v>
       </c>
       <c r="O245" s="4" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="P245" s="4" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -32848,128 +32872,128 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -32997,62 +33021,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>2.5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="B5" s="15" t="n">
         <v>400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>150</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
